--- a/diseases/d058/2010-2014.xlsx
+++ b/diseases/d058/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>23</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.04716078490514505</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>13</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.02665609581595155</v>
       </c>
@@ -1801,9 +1795,6 @@
       <c r="O9" t="n">
         <v>11</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.02255515799811285</v>
       </c>
@@ -2245,9 +2236,6 @@
       <c r="O12" t="n">
         <v>16</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.0328075025427096</v>
       </c>
@@ -2689,9 +2677,6 @@
       <c r="O15" t="n">
         <v>27</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.05536266054082245</v>
       </c>
@@ -3133,9 +3118,6 @@
       <c r="O18" t="n">
         <v>27</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.05536266054082245</v>
       </c>
@@ -3577,9 +3559,6 @@
       <c r="O21" t="n">
         <v>27</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.05536266054082245</v>
       </c>
@@ -4021,9 +4000,6 @@
       <c r="O24" t="n">
         <v>27</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.05536266054082245</v>
       </c>
@@ -4465,9 +4441,6 @@
       <c r="O27" t="n">
         <v>60</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.123028134535161</v>
       </c>
@@ -4909,9 +4882,6 @@
       <c r="O30" t="n">
         <v>1203</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>2.466714097429978</v>
       </c>
@@ -5353,9 +5323,6 @@
       <c r="O33" t="n">
         <v>3832</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>7.857396858978949</v>
       </c>
@@ -5797,9 +5764,6 @@
       <c r="O36" t="n">
         <v>405</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.8304399081123368</v>
       </c>
@@ -6241,9 +6205,6 @@
       <c r="O39" t="n">
         <v>37</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.07531401338230277</v>
       </c>
@@ -6685,9 +6646,6 @@
       <c r="O42" t="n">
         <v>11</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.0223906526271711</v>
       </c>
@@ -7129,9 +7087,6 @@
       <c r="O45" t="n">
         <v>10</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.02035513875197372</v>
       </c>
@@ -7573,9 +7528,6 @@
       <c r="O48" t="n">
         <v>13</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.02646168037756584</v>
       </c>
@@ -8017,9 +7969,6 @@
       <c r="O51" t="n">
         <v>25</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.05088784687993431</v>
       </c>
@@ -8461,9 +8410,6 @@
       <c r="O54" t="n">
         <v>24</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.04885233300473694</v>
       </c>
@@ -8905,9 +8851,6 @@
       <c r="O57" t="n">
         <v>18</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.03663924975355271</v>
       </c>
@@ -9349,9 +9292,6 @@
       <c r="O60" t="n">
         <v>28</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.05699438850552643</v>
       </c>
@@ -9793,9 +9733,6 @@
       <c r="O63" t="n">
         <v>77</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.1567345683901977</v>
       </c>
@@ -10237,9 +10174,6 @@
       <c r="O66" t="n">
         <v>1825</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>3.714812822235205</v>
       </c>
@@ -10681,9 +10615,6 @@
       <c r="O69" t="n">
         <v>2718</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>5.532526712786458</v>
       </c>
@@ -11125,9 +11056,6 @@
       <c r="O72" t="n">
         <v>365</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.7429625644470409</v>
       </c>
@@ -11569,9 +11497,6 @@
       <c r="O75" t="n">
         <v>51</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.1028234523641476</v>
       </c>
@@ -12013,9 +11938,6 @@
       <c r="O78" t="n">
         <v>41</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.08266199111627549</v>
       </c>
@@ -12457,9 +12379,6 @@
       <c r="O81" t="n">
         <v>15</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.03024219187180811</v>
       </c>
@@ -12901,9 +12820,6 @@
       <c r="O84" t="n">
         <v>17</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.03427448412138252</v>
       </c>
@@ -13345,9 +13261,6 @@
       <c r="O87" t="n">
         <v>20</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.04032292249574414</v>
       </c>
@@ -13789,9 +13702,6 @@
       <c r="O90" t="n">
         <v>14</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.0282260457470209</v>
       </c>
@@ -14233,9 +14143,6 @@
       <c r="O93" t="n">
         <v>25</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.05040365311968018</v>
       </c>
@@ -14677,9 +14584,6 @@
       <c r="O96" t="n">
         <v>36</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.07258126049233946</v>
       </c>
@@ -15121,9 +15025,6 @@
       <c r="O99" t="n">
         <v>102</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.2056469047282951</v>
       </c>
@@ -16009,9 +15910,6 @@
       <c r="O105" t="n">
         <v>3680</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>7.419417739216922</v>
       </c>
@@ -17045,9 +16943,6 @@
       <c r="O112" t="n">
         <v>4341</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>8.752090327701266</v>
       </c>
@@ -18229,9 +18124,6 @@
       <c r="O120" t="n">
         <v>262</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.5282302846942483</v>
       </c>
@@ -19265,9 +19157,6 @@
       <c r="O127" t="n">
         <v>25</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.0499289366437643</v>
       </c>
@@ -20449,9 +20338,6 @@
       <c r="O135" t="n">
         <v>16</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.03195451945200915</v>
       </c>
@@ -21485,9 +21371,6 @@
       <c r="O142" t="n">
         <v>6</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01198294479450343</v>
       </c>
@@ -22521,9 +22404,6 @@
       <c r="O149" t="n">
         <v>9</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.01797441719175515</v>
       </c>
@@ -23557,9 +23437,6 @@
       <c r="O156" t="n">
         <v>30</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.05991472397251715</v>
       </c>
@@ -24741,9 +24618,6 @@
       <c r="O164" t="n">
         <v>31</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.06191188143826773</v>
       </c>
@@ -25777,9 +25651,6 @@
       <c r="O171" t="n">
         <v>39</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.0778891411642723</v>
       </c>
@@ -26813,9 +26684,6 @@
       <c r="O178" t="n">
         <v>26</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.05192609410951488</v>
       </c>
@@ -27997,9 +27865,6 @@
       <c r="O186" t="n">
         <v>75</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.1497868099312929</v>
       </c>
@@ -29033,9 +28898,6 @@
       <c r="O193" t="n">
         <v>3656</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>7.30160769478409</v>
       </c>
@@ -30217,9 +30079,6 @@
       <c r="O201" t="n">
         <v>6042</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>12.06682540806496</v>
       </c>
@@ -31253,9 +31112,6 @@
       <c r="O208" t="n">
         <v>410</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.8188345609577344</v>
       </c>
@@ -32289,9 +32145,6 @@
       <c r="O215" t="n">
         <v>34</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.06727470401578835</v>
       </c>
@@ -33473,9 +33326,6 @@
       <c r="O223" t="n">
         <v>12</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.02374401318204294</v>
       </c>
@@ -34509,9 +34359,6 @@
       <c r="O230" t="n">
         <v>19</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.03759468753823466</v>
       </c>
@@ -35545,9 +35392,6 @@
       <c r="O237" t="n">
         <v>27</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.05342402965959663</v>
       </c>
@@ -36581,9 +36425,6 @@
       <c r="O244" t="n">
         <v>45</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.08904004943266104</v>
       </c>
@@ -37765,9 +37606,6 @@
       <c r="O252" t="n">
         <v>27</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.05342402965959663</v>
       </c>
@@ -38801,9 +38639,6 @@
       <c r="O259" t="n">
         <v>37</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.07321070731129908</v>
       </c>
@@ -39985,9 +39820,6 @@
       <c r="O267" t="n">
         <v>47</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.09299738496300154</v>
       </c>
@@ -41021,9 +40853,6 @@
       <c r="O274" t="n">
         <v>259</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.5124749511790936</v>
       </c>
@@ -42057,9 +41886,6 @@
       <c r="O281" t="n">
         <v>4066</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>8.045263133182218</v>
       </c>
@@ -43241,9 +43067,6 @@
       <c r="O289" t="n">
         <v>3302</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>6.533560960592149</v>
       </c>
@@ -44276,9 +44099,6 @@
       </c>
       <c r="O296" t="n">
         <v>255</v>
-      </c>
-      <c r="Q296" t="n">
-        <v>0</v>
       </c>
       <c r="R296" t="n">
         <v>0.5045602801184126</v>
